--- a/2026-10-09 Working with Data in Excel/Bookstore_Workshop_Dataset.xlsx
+++ b/2026-10-09 Working with Data in Excel/Bookstore_Workshop_Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://outlookuga-my.sharepoint.com/personal/ksb89187_uga_edu/Documents/Documents/OSDS/Workshops and Talks/2026-10-09 Working with Data in Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_07128DC31768C82FEB06F4F7415DCE3A6747C4EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B620B2-27CB-4823-AF85-3846BBC5A4B0}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_07128DC31768C82FEB06F4F7415DCE3A6747C4EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A26B668C-4258-4BAD-BD0D-AB43E4CB1BA8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookstoreOrders" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="184">
   <si>
     <t>OrderID</t>
   </si>
@@ -1090,12 +1090,7 @@
       <c r="H4" s="3">
         <v>46175</v>
       </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1643,10 +1638,10 @@
         <v>46188</v>
       </c>
       <c r="I23" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="J23" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="K23" s="4"/>
     </row>
@@ -1933,10 +1928,10 @@
         <v>46194</v>
       </c>
       <c r="I33" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="J33" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="K33" s="4"/>
     </row>
@@ -3121,7 +3116,7 @@
         <v>46221</v>
       </c>
       <c r="I74" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="J74" s="4">
         <v>0.1</v>
@@ -3382,12 +3377,7 @@
       <c r="H83" s="3">
         <v>46227</v>
       </c>
-      <c r="I83" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="J83" s="4"/>
       <c r="K83" s="4"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -3757,7 +3747,7 @@
         <v>46235</v>
       </c>
       <c r="I96" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="J96" s="4">
         <v>0.1</v>
@@ -3901,7 +3891,12 @@
       <c r="H101" s="3">
         <v>46239</v>
       </c>
-      <c r="J101" s="4"/>
+      <c r="I101" t="s">
+        <v>20</v>
+      </c>
+      <c r="J101" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K101" s="4"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3929,12 +3924,7 @@
       <c r="H102" s="3">
         <v>46239</v>
       </c>
-      <c r="I102" t="s">
-        <v>20</v>
-      </c>
-      <c r="J102" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="J102" s="4"/>
       <c r="K102" s="4"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -3962,7 +3952,12 @@
       <c r="H103" s="3">
         <v>46240</v>
       </c>
-      <c r="J103" s="4"/>
+      <c r="I103" t="s">
+        <v>20</v>
+      </c>
+      <c r="J103" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K103" s="4"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -4051,7 +4046,12 @@
       <c r="H106" s="3">
         <v>46242</v>
       </c>
-      <c r="J106" s="4"/>
+      <c r="I106" t="s">
+        <v>20</v>
+      </c>
+      <c r="J106" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K106" s="4"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -4281,7 +4281,7 @@
         <v>46247</v>
       </c>
       <c r="I114" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="J114" s="4">
         <v>0.1</v>
@@ -4313,7 +4313,12 @@
       <c r="H115" s="3">
         <v>46248</v>
       </c>
-      <c r="J115" s="4"/>
+      <c r="I115" t="s">
+        <v>20</v>
+      </c>
+      <c r="J115" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K115" s="4"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -4341,7 +4346,12 @@
       <c r="H116" s="3">
         <v>46248</v>
       </c>
-      <c r="J116" s="4"/>
+      <c r="I116" t="s">
+        <v>20</v>
+      </c>
+      <c r="J116" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K116" s="4"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -4402,7 +4412,12 @@
       <c r="H118" s="3">
         <v>46250</v>
       </c>
-      <c r="J118" s="4"/>
+      <c r="I118" t="s">
+        <v>20</v>
+      </c>
+      <c r="J118" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K118" s="4"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -4514,12 +4529,7 @@
       <c r="H122" s="3">
         <v>46252</v>
       </c>
-      <c r="I122" t="s">
-        <v>20</v>
-      </c>
-      <c r="J122" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="J122" s="4"/>
       <c r="K122" s="4"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -4754,10 +4764,10 @@
         <v>46258</v>
       </c>
       <c r="I130" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="J130" s="4">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="K130" s="4"/>
     </row>
@@ -4814,7 +4824,12 @@
       <c r="H132" s="3">
         <v>46259</v>
       </c>
-      <c r="J132" s="4"/>
+      <c r="I132" t="s">
+        <v>20</v>
+      </c>
+      <c r="J132" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K132" s="4"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -4982,7 +4997,12 @@
       <c r="H138" s="3">
         <v>46263</v>
       </c>
-      <c r="J138" s="4"/>
+      <c r="I138" t="s">
+        <v>20</v>
+      </c>
+      <c r="J138" s="4">
+        <v>0.05</v>
+      </c>
       <c r="K138" s="4"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -5693,10 +5713,10 @@
         <v>46279</v>
       </c>
       <c r="I163" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="J163" s="4">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="K163" s="4"/>
     </row>
